--- a/y11628/output/commission_report.xlsx
+++ b/y11628/output/commission_report.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -526,44 +526,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>硬件设备</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>62823.72</v>
+        <v>272621.99</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1884.7116</v>
+        <v>26989.57701</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1884.7116</v>
+        <v>26989.57701</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>待人工确认</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '硬件设备' 不在区域 '华南区' 允许范围内, 需人工确认</t>
+          <t>计算正常</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -580,25 +580,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>西北区</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>解决方案</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>485232.89</v>
+        <v>309369.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -608,26 +608,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>43670.9601</v>
+        <v>27224.49576</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-13612.24788</v>
       </c>
       <c r="K3" t="n">
-        <v>43670.9601</v>
+        <v>13612.24788</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>回款未达标</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>回款未达标: 状态='未回款', 已回款 87897.46 (18.1%); 回款逾期 14 天 (要求 45 天内)</t>
+          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 92810.78 (30.0%); 费率版本不匹配: 订单指定版本 '2024Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>钱七</t>
+          <t>孙八</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -654,15 +654,15 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>云服务</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>497668</v>
+        <v>275659.08</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>29860.08</v>
+        <v>13645.12446</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>29860.08</v>
+        <v>13645.12446</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -708,54 +708,54 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>西南区</t>
+          <t>华南区</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185677.56</v>
+        <v>466124.86</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>12997.4292</v>
+        <v>23073.18057</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12997.4292</v>
+        <v>23073.18057</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>计算正常</t>
+          <t>跨区销售警告: 产品线 '硬件设备' 不在区域 '华南区' 允许范围内, 需人工确认; 回款逾期 49 天 (要求 45 天内)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -772,54 +772,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>企业软件</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>201326.85</v>
+        <v>265947.16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2024Q2</t>
-        </is>
-      </c>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>18119.4165</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-20132.685</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-2013.268500000002</v>
+        <v>0</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>跨区销售</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '咨询服务' 不属区域 '华东区', 已扣除罚金 20132.69 (10.0%)</t>
+          <t>区域 '华东' 未在规则表中定义</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -841,20 +833,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>386903.61</v>
+        <v>263647.95</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -864,26 +856,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>34821.3249</v>
+        <v>13050.573525</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34821.3249</v>
+        <v>13050.573525</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>待人工确认</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>计算正常</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -900,25 +892,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>西南区</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>企业软件</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>253978.49</v>
+        <v>200867.16</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -928,17 +920,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>20318.2792</v>
+        <v>15466.77132</v>
       </c>
       <c r="J8" t="n">
-        <v>-25397.849</v>
+        <v>-37863.45966</v>
       </c>
       <c r="K8" t="n">
-        <v>-5079.569800000001</v>
+        <v>-22396.68834</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -947,7 +939,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '解决方案' 不属区域 '华东区', 已扣除罚金 25397.85 (10.0%)</t>
+          <t>跨区销售: 产品线 '企业软件' 不属区域 '西南区', 已扣除罚金 30130.07 (15.0%); 回款未达标: 状态='未回款', 已回款 67417.22 (33.6%)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -964,25 +956,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>钱七</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>西南区</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>236180.82</v>
+        <v>209197.46</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -992,26 +984,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>16532.6574</v>
+        <v>20710.54854</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>16532.6574</v>
+        <v>20710.54854</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>费率版本错</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>回款逾期 28 天 (要求 60 天内)</t>
+          <t>费率版本不匹配: 订单指定版本 '2024Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1028,54 +1020,54 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>吴十</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220670.07</v>
+        <v>108725.81</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>50000-200000</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>17653.6056</v>
+        <v>3587.95173</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-1793.975865</v>
       </c>
       <c r="K10" t="n">
-        <v>17653.6056</v>
+        <v>1793.975865</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>回款未达标</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>计算正常</t>
+          <t>回款未达标: 状态='未回款', 已回款 73531.84 (67.6%)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1092,12 +1084,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>吴十</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>西北区</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1106,11 +1098,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103916.64</v>
+        <v>132357.77</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1120,26 +1112,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7274.1648</v>
+        <v>10191.54829</v>
       </c>
       <c r="J11" t="n">
-        <v>-10391.664</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-3117.4992</v>
+        <v>10191.54829</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>跨区销售</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '咨询服务' 不属区域 '华东区', 已扣除罚金 10391.66 (10.0%)</t>
+          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>吴十</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1170,31 +1162,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>241176.78</v>
+        <v>54093</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>50000-200000</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2024Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>21705.9102</v>
+        <v>4165.161</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-2082.5805</v>
       </c>
       <c r="K12" t="n">
-        <v>21705.9102</v>
+        <v>2082.5805</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1203,7 +1195,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 34403.03 (63.6%); 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1230,35 +1222,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>云服务</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>74553.72</v>
+        <v>48867.89</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>0-50000</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3727.686</v>
+        <v>1075.09358</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3727.686</v>
+        <v>1075.09358</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1267,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>计算正常</t>
+          <t>回款逾期 22 天 (要求 60 天内)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1284,7 +1276,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1298,11 +1290,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>204527.36</v>
+        <v>348918.98</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1312,26 +1304,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>12271.6416</v>
+        <v>23028.65268</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-11514.32634</v>
       </c>
       <c r="K14" t="n">
-        <v>12271.6416</v>
+        <v>11514.32634</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>回款未达标</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '云服务' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 136551.11 (66.8%); 回款逾期 1 天 (要求 60 天内)</t>
+          <t>跨区销售警告: 产品线 '云服务' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 174459.49 (50.0%); 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1353,49 +1345,49 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>西北区</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>431438.65</v>
+        <v>38988.21</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>0-50000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>30200.7055</v>
+        <v>2144.35155</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>30200.7055</v>
+        <v>2144.35155</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>回款逾期 3 天 (要求 60 天内)</t>
+          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1422,11 +1414,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>解决方案</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39097.58</v>
+        <v>456642.95</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1468,54 +1460,54 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>孙八</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>西南区</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>398337.75</v>
+        <v>89980.34</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>50000-200000</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2024Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>31867.02</v>
+        <v>2969.35122</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-14981.72661</v>
       </c>
       <c r="K17" t="n">
-        <v>31867.02</v>
+        <v>-12012.37539</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>待人工确认</t>
+          <t>费率版本错</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>跨区销售: 产品线 '硬件设备' 不属区域 '西南区', 已扣除罚金 13497.05 (15.0%); 回款未达标: 状态='未回款', 已回款 53094.24 (59.0%); 费率版本不匹配: 订单指定版本 '2024Q1' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1537,7 +1529,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>华南区</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1546,11 +1538,11 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>450650.94</v>
+        <v>294119.38</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1560,26 +1552,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>20279.2923</v>
+        <v>14558.90931</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>20279.2923</v>
+        <v>14558.90931</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>计算正常</t>
+          <t>跨区销售警告: 产品线 '硬件设备' 不在区域 '华南区' 允许范围内, 需人工确认; 回款逾期 66 天 (要求 45 天内); 费率版本不匹配: 订单指定版本 '2024Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1596,7 +1588,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1610,11 +1602,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>270254.19</v>
+        <v>433532.31</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1624,17 +1616,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>16215.2514</v>
+        <v>28613.13246</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>16215.2514</v>
+        <v>28613.13246</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1665,49 +1657,49 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>硬件设备</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>110245.47</v>
+        <v>449894.87</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3307.3641</v>
+        <v>44539.59213</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-22269.796065</v>
       </c>
       <c r="K20" t="n">
-        <v>3307.3641</v>
+        <v>22269.796065</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>回款未达标</t>
+          <t>费率版本错</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>回款未达标: 状态='未回款', 已回款 30976.38 (28.1%)</t>
+          <t>回款未达标: 状态='未回款', 已回款 0.00 (0.0%); 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1724,54 +1716,54 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>孙八</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>西南区</t>
+          <t>西北区</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>解决方案</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>283672.4</v>
+        <v>13716.1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>0-50000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>19857.068</v>
+        <v>603.5083999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>-42550.86</v>
+        <v>-301.7542</v>
       </c>
       <c r="K21" t="n">
-        <v>-22693.792</v>
+        <v>301.7542</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>跨区销售</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '企业软件' 不属区域 '西南区', 已扣除罚金 42550.86 (15.0%)</t>
+          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 2592.97 (18.9%); 回款逾期 14 天 (要求 60 天内); 费率版本不匹配: 订单指定版本 '2024Q1' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1788,12 +1780,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1802,40 +1794,40 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>128399.31</v>
+        <v>20774.93</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>0-50000</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5135.9724</v>
+        <v>457.04846</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-1038.7465</v>
       </c>
       <c r="K22" t="n">
-        <v>5135.9724</v>
+        <v>-581.69804</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>待人工确认</t>
+          <t>跨区销售</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '云服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>跨区销售: 产品线 '云服务' 不属区域 '华北区', 已扣除罚金 1038.75 (5.0%)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1852,7 +1844,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>吴十</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,31 +1858,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>177839.74</v>
+        <v>472131.43</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10670.3844</v>
+        <v>41547.56584</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>10670.3844</v>
+        <v>41547.56584</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1899,7 +1891,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认; 回款逾期 11 天 (要求 60 天内); 费率版本不匹配: 订单指定版本 '2026Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1916,7 +1908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>钱七</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1930,31 +1922,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>187798.2</v>
+        <v>16950.32</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>0-50000</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11267.892</v>
+        <v>745.81408</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>11267.892</v>
+        <v>745.81408</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1963,7 +1955,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认; 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1980,25 +1972,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>华南区</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>云服务</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220420.33</v>
+        <v>207088.97</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2008,26 +2000,26 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>15429.4231</v>
+        <v>13667.87202</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>15429.4231</v>
+        <v>13667.87202</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>计算正常</t>
+          <t>跨区销售警告: 产品线 '云服务' 不在区域 '华南区' 允许范围内, 需人工确认</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2054,44 +2046,36 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>硬件设备</t>
+          <t>硬件</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>285940.35</v>
+        <v>157376</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>12867.31575</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-15737.6</v>
       </c>
       <c r="K26" t="n">
-        <v>12867.31575</v>
+        <v>-15737.6</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>错误</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>回款逾期 45 天 (要求 60 天内)</t>
+          <t>跨区销售: 产品线 '硬件' 不属区域 '华东区', 已扣除罚金 15737.60 (10.0%); 回款未达标: 状态='未回款', 已回款 89306.63 (56.7%); 产品线 '硬件' 无对应的费率配置</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2108,54 +2092,54 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>西南区</t>
+          <t>华东区</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>149974.19</v>
+        <v>214011.57</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>8998.4514</v>
+        <v>10593.572715</v>
       </c>
       <c r="J27" t="n">
-        <v>-22496.1285</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>-13497.6771</v>
+        <v>10593.572715</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>跨区销售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '解决方案' 不属区域 '西南区', 已扣除罚金 22496.13 (15.0%)</t>
+          <t>计算正常</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2172,54 +2156,54 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>西南区</t>
+          <t>华东区</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>云服务</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>300582.86</v>
+        <v>57290.17</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>50000-200000</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>24046.6288</v>
+        <v>2520.76748</v>
       </c>
       <c r="J28" t="n">
-        <v>-45087.429</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>-21040.8002</v>
+        <v>2520.76748</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>跨区销售</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '解决方案' 不属区域 '西南区', 已扣除罚金 45087.43 (15.0%)</t>
+          <t>计算正常</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2236,25 +2220,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>云服务</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>274263.02</v>
+        <v>384475.71</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2264,26 +2248,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>19198.4114</v>
+        <v>25375.39686</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-19223.7855</v>
       </c>
       <c r="K29" t="n">
-        <v>19198.4114</v>
+        <v>6151.611360000003</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>费率版本错</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>计算正常</t>
+          <t>跨区销售: 产品线 '云服务' 不属区域 '华北区', 已扣除罚金 19223.79 (5.0%); 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2300,12 +2284,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>西南区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2314,11 +2298,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>359097.36</v>
+        <v>393116.12</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2328,17 +2312,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2024Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>32318.7624</v>
+        <v>38918.49588</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>32318.7624</v>
+        <v>38918.49588</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2364,54 +2348,54 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>吴十</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>西南区</t>
+          <t>华南区</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6107.07</v>
+        <v>251495.42</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0-50000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>244.2828</v>
+        <v>12449.02329</v>
       </c>
       <c r="J31" t="n">
-        <v>-916.0604999999999</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>-671.7777</v>
+        <v>12449.02329</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>跨区销售</t>
+          <t>待人工确认</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '解决方案' 不属区域 '西南区', 已扣除罚金 916.06 (15.0%)</t>
+          <t>跨区销售警告: 产品线 '硬件设备' 不在区域 '华南区' 允许范围内, 需人工确认; 费率版本不匹配: 订单指定版本 '2026Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2431,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2504,7 +2488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD0003</t>
+          <t>ORD0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2514,20 +2498,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>华南区</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>云服务</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>497668</v>
+        <v>272621.99</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2537,17 +2521,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>29860.08</v>
+        <v>26989.57701</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>29860.08</v>
+        <v>26989.57701</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -2563,7 +2547,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD0004</t>
+          <t>ORD0003</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2573,40 +2557,40 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>西南区</t>
+          <t>华东区</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185677.56</v>
+        <v>275659.08</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>12997.4292</v>
+        <v>13645.12446</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>12997.4292</v>
+        <v>13645.12446</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -2622,30 +2606,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD0008</t>
+          <t>ORD0006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>钱七</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>236180.82</v>
+        <v>263647.95</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2655,17 +2639,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>16532.6574</v>
+        <v>13050.573525</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>16532.6574</v>
+        <v>13050.573525</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -2674,57 +2658,57 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>回款逾期 28 天 (要求 60 天内)</t>
+          <t>计算正常</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD0009</t>
+          <t>ORD0012</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>吴十</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>华东区</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>云服务</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220670.07</v>
+        <v>48867.89</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>0-50000</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024Q1</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>17653.6056</v>
+        <v>1075.09358</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>17653.6056</v>
+        <v>1075.09358</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -2733,19 +2717,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>计算正常</t>
+          <t>回款逾期 22 天 (要求 60 天内)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD0012</t>
+          <t>ORD0026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2755,11 +2739,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>74553.72</v>
+        <v>214011.57</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2768,22 +2752,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3727.686</v>
+        <v>10593.572715</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3727.686</v>
+        <v>10593.572715</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -2799,12 +2783,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD0014</t>
+          <t>ORD0027</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>钱七</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2814,35 +2798,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>云服务</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>431438.65</v>
+        <v>57290.17</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>50000-200000</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>30200.7055</v>
+        <v>2520.76748</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>30200.7055</v>
+        <v>2520.76748</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -2851,37 +2835,37 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>回款逾期 3 天 (要求 60 天内)</t>
+          <t>计算正常</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD0017</t>
+          <t>ORD0029</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>硬件设备</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>450650.94</v>
+        <v>393116.12</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2891,17 +2875,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>20279.2923</v>
+        <v>38918.49588</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20279.2923</v>
+        <v>38918.49588</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -2909,242 +2893,6 @@
         </is>
       </c>
       <c r="M8" t="inlineStr">
-        <is>
-          <t>计算正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ORD0024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>企业软件</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>220420.33</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>7.0%</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>15429.4231</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>15429.4231</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>计算正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ORD0025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>吴十</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>硬件设备</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>285940.35</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>12867.31575</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>12867.31575</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>回款逾期 45 天 (要求 60 天内)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ORD0028</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>西北区</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>企业软件</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>274263.02</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>7.0%</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>19198.4114</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>19198.4114</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>计算正常</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ORD0029</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>西南区</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>咨询服务</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>359097.36</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2024Q2</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>32318.7624</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>32318.7624</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
         <is>
           <t>计算正常</t>
         </is>
@@ -3197,7 +2945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3270,50 +3018,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD0001</t>
+          <t>ORD0002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>西北区</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>硬件设备</t>
+          <t>解决方案</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>62823.72</v>
+        <v>309369.27</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>200000-500000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1884.7116</v>
+        <v>27224.49576</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-13612.24788</v>
       </c>
       <c r="K2" t="n">
-        <v>1884.7116</v>
+        <v>13612.24788</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -3322,37 +3070,37 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '硬件设备' 不在区域 '华南区' 允许范围内, 需人工确认</t>
+          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 92810.78 (30.0%); 费率版本不匹配: 订单指定版本 '2024Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD0006</t>
+          <t>ORD0004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周九</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>华南区</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>386903.61</v>
+        <v>466124.86</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3362,17 +3110,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>34821.3249</v>
+        <v>23073.18057</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>34821.3249</v>
+        <v>23073.18057</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -3381,57 +3129,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>跨区销售警告: 产品线 '硬件设备' 不在区域 '华南区' 允许范围内, 需人工确认; 回款逾期 49 天 (要求 45 天内)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD0011</t>
+          <t>ORD0005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>吴十</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>企业软件</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>241176.78</v>
+        <v>265947.16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2024Q2</t>
-        </is>
-      </c>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>21705.9102</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>21705.9102</v>
+        <v>0</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -3440,14 +3180,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>区域 '华东' 未在规则表中定义</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD0015</t>
+          <t>ORD0010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3457,32 +3197,40 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>华南北区</t>
+          <t>西北区</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>企业软件</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39097.58</v>
+        <v>132357.77</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>50000-200000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>10191.54829</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>10191.54829</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -3491,19 +3239,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>区域 '华南北区' 未在规则表中定义</t>
+          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD0016</t>
+          <t>ORD0011</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3513,35 +3261,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>398337.75</v>
+        <v>54093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>50000-200000</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>31867.02</v>
+        <v>4165.161</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-2082.5805</v>
       </c>
       <c r="K6" t="n">
-        <v>31867.02</v>
+        <v>2082.5805</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -3550,24 +3298,24 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 34403.03 (63.6%); 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD0018</t>
+          <t>ORD0013</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>西北区</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -3576,11 +3324,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>270254.19</v>
+        <v>348918.98</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3590,17 +3338,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>16215.2514</v>
+        <v>23028.65268</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-11514.32634</v>
       </c>
       <c r="K7" t="n">
-        <v>16215.2514</v>
+        <v>11514.32634</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -3609,19 +3357,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '云服务' 不在区域 '华南区' 允许范围内, 需人工确认</t>
+          <t>跨区销售警告: 产品线 '云服务' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 174459.49 (50.0%); 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD0021</t>
+          <t>ORD0014</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3631,35 +3379,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>云服务</t>
+          <t>咨询服务</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>128399.31</v>
+        <v>38988.21</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50000-200000</t>
+          <t>0-50000</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5135.9724</v>
+        <v>2144.35155</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5135.9724</v>
+        <v>2144.35155</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -3668,14 +3416,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '云服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>跨区销售警告: 产品线 '咨询服务' 不在区域 '西北区' 允许范围内, 需人工确认</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD0022</t>
+          <t>ORD0015</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3685,7 +3433,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>西北区</t>
+          <t>华南北区</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3694,31 +3442,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>177839.74</v>
+        <v>456642.95</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>50000-200000</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>10670.3844</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>10670.3844</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -3727,66 +3467,420 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+          <t>区域 '华南北区' 未在规则表中定义</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>ORD0017</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>硬件设备</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>294119.38</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>200000-500000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>14558.90931</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>14558.90931</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>待人工确认</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>跨区销售警告: 产品线 '硬件设备' 不在区域 '华南区' 允许范围内, 需人工确认; 回款逾期 66 天 (要求 45 天内); 费率版本不匹配: 订单指定版本 '2024Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORD0018</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>云服务</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>433532.31</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>200000-500000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>28613.13246</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28613.13246</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>待人工确认</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>跨区销售警告: 产品线 '云服务' 不在区域 '华南区' 允许范围内, 需人工确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ORD0020</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>西北区</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>解决方案</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>13716.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0-50000</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>603.5083999999999</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-301.7542</v>
+      </c>
+      <c r="K12" t="n">
+        <v>301.7542</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>待人工确认</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 2592.97 (18.9%); 回款逾期 14 天 (要求 60 天内); 费率版本不匹配: 订单指定版本 '2024Q1' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ORD0022</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>西北区</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>解决方案</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>472131.43</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>200000-500000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>41547.56584</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>41547.56584</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>待人工确认</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认; 回款逾期 11 天 (要求 60 天内); 费率版本不匹配: 订单指定版本 '2026Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>ORD0023</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>西北区</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>解决方案</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>187798.2</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>50000-200000</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2024Q1</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>11267.892</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>11267.892</v>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="E14" t="n">
+        <v>16950.32</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0-50000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>745.81408</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>745.81408</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>待人工确认</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>跨区销售警告: 产品线 '解决方案' 不在区域 '西北区' 允许范围内, 需人工确认; 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ORD0024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>云服务</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>207088.97</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>200000-500000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>13667.87202</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>13667.87202</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>待人工确认</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>跨区销售警告: 产品线 '云服务' 不在区域 '华南区' 允许范围内, 需人工确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ORD0030</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>吴十</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>华南区</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>硬件设备</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>251495.42</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>200000-500000</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>12449.02329</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12449.02329</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>待人工确认</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>跨区销售警告: 产品线 '硬件设备' 不在区域 '华南区' 允许范围内, 需人工确认; 费率版本不匹配: 订单指定版本 '2026Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3874,30 +3968,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD0005</t>
+          <t>ORD0007</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>西南区</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>企业软件</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>201326.85</v>
+        <v>200867.16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3907,17 +4001,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024Q2</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>18119.4165</v>
+        <v>15466.77132</v>
       </c>
       <c r="J2" t="n">
-        <v>-20132.685</v>
+        <v>-37863.45966</v>
       </c>
       <c r="K2" t="n">
-        <v>-2013.268500000002</v>
+        <v>-22396.68834</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -3926,57 +4020,57 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '咨询服务' 不属区域 '华东区', 已扣除罚金 20132.69 (10.0%)</t>
+          <t>跨区销售: 产品线 '企业软件' 不属区域 '西南区', 已扣除罚金 30130.07 (15.0%); 回款未达标: 状态='未回款', 已回款 67417.22 (33.6%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD0007</t>
+          <t>ORD0021</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>华东区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>解决方案</t>
+          <t>云服务</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>253978.49</v>
+        <v>20774.93</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>0-50000</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>20318.2792</v>
+        <v>457.04846</v>
       </c>
       <c r="J3" t="n">
-        <v>-25397.849</v>
+        <v>-1038.7465</v>
       </c>
       <c r="K3" t="n">
-        <v>-5079.569800000001</v>
+        <v>-581.69804</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -3985,302 +4079,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>跨区销售: 产品线 '解决方案' 不属区域 '华东区', 已扣除罚金 25397.85 (10.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ORD0010</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>华东区</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>咨询服务</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>103916.64</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>7.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>50000-200000</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>7274.1648</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-10391.664</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-3117.4992</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>跨区销售</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>跨区销售: 产品线 '咨询服务' 不属区域 '华东区', 已扣除罚金 10391.66 (10.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ORD0020</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>西南区</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>企业软件</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>283672.4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>7.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>19857.068</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-42550.86</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-22693.792</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>跨区销售</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>跨区销售: 产品线 '企业软件' 不属区域 '西南区', 已扣除罚金 42550.86 (15.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ORD0026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>西南区</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>解决方案</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>149974.19</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>50000-200000</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>8998.4514</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-22496.1285</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-13497.6771</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>跨区销售</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>跨区销售: 产品线 '解决方案' 不属区域 '西南区', 已扣除罚金 22496.13 (15.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ORD0027</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>西南区</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>解决方案</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>300582.86</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>8.0%</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>24046.6288</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-45087.429</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-21040.8002</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>跨区销售</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>跨区销售: 产品线 '解决方案' 不属区域 '西南区', 已扣除罚金 45087.43 (15.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ORD0030</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>孙八</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>西南区</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>解决方案</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6107.07</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>4.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0-50000</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2024Q1</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>244.2828</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-916.0604999999999</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-671.7777</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>跨区销售</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>跨区销售: 产品线 '解决方案' 不属区域 '西南区', 已扣除罚金 916.06 (15.0%)</t>
+          <t>跨区销售: 产品线 '云服务' 不属区域 '华北区', 已扣除罚金 1038.75 (5.0%)</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4368,50 +4167,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD0002</t>
+          <t>ORD0009</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>华南区</t>
+          <t>华北区</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>咨询服务</t>
+          <t>硬件设备</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>485232.89</v>
+        <v>108725.81</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>200000-500000</t>
+          <t>50000-200000</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023Q4</t>
+          <t>2026Q1</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>43670.9601</v>
+        <v>3587.95173</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-1793.975865</v>
       </c>
       <c r="K2" t="n">
-        <v>43670.9601</v>
+        <v>1793.975865</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4420,125 +4219,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>回款未达标: 状态='未回款', 已回款 87897.46 (18.1%); 回款逾期 14 天 (要求 45 天内)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ORD0013</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>西北区</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>云服务</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>204527.36</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>200000-500000</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2023Q4</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>12271.6416</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>12271.6416</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>回款未达标</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>跨区销售警告: 产品线 '云服务' 不在区域 '西北区' 允许范围内, 需人工确认; 回款未达标: 状态='未回款', 已回款 136551.11 (66.8%); 回款逾期 1 天 (要求 60 天内)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ORD0019</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>西北区</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>硬件设备</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>110245.47</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>50000-200000</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2024Q1</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3307.3641</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3307.3641</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>回款未达标</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>回款未达标: 状态='未回款', 已回款 30976.38 (28.1%)</t>
+          <t>回款未达标: 状态='未回款', 已回款 73531.84 (67.6%)</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4569,12 +4250,293 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>订单金额</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>适用费率</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>阶梯区间</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>费率版本</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>调整前佣金</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>调整金额</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>最终佣金</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ORD0008</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>西南区</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>咨询服务</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>209197.46</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>200000-500000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>20710.54854</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20710.54854</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>费率版本错</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>费率版本不匹配: 订单指定版本 '2024Q2' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ORD0016</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>西南区</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>硬件设备</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>89980.34</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>50000-200000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2969.35122</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-14981.72661</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-12012.37539</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>费率版本错</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>跨区销售: 产品线 '硬件设备' 不属区域 '西南区', 已扣除罚金 13497.05 (15.0%); 回款未达标: 状态='未回款', 已回款 53094.24 (59.0%); 费率版本不匹配: 订单指定版本 '2024Q1' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ORD0019</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>华北区</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>咨询服务</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>449894.87</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9.9%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>200000-500000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>44539.59213</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-22269.796065</v>
+      </c>
+      <c r="K4" t="n">
+        <v>22269.796065</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>费率版本错</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>回款未达标: 状态='未回款', 已回款 0.00 (0.0%); 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ORD0028</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>华北区</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>云服务</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>384475.71</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6.6%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>200000-500000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>25375.39686</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-19223.7855</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6151.611360000003</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>费率版本错</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>跨区销售: 产品线 '云服务' 不属区域 '华北区', 已扣除罚金 19223.79 (5.0%); 费率版本不匹配: 订单指定版本 '2023Q4' 不在目标季度 2026Q1 范围内, 将使用对应季度版本</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4605,12 +4567,108 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>产品线</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>订单金额</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>适用费率</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>阶梯区间</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>费率版本</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>调整前佣金</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>调整金额</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>最终佣金</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ORD0025</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>吴十</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>华东区</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>硬件</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>157376</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-15737.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-15737.6</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>跨区销售: 产品线 '硬件' 不属区域 '华东区', 已扣除罚金 15737.60 (10.0%); 回款未达标: 状态='未回款', 已回款 89306.63 (56.7%); 产品线 '硬件' 无对应的费率配置</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4663,20 +4721,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>赵六</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>329726.16</v>
+        <v>359937.59</v>
       </c>
       <c r="D2" t="n">
-        <v>3122.703899999998</v>
+        <v>16379.81697</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -4685,64 +4743,64 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>钱七</t>
+          <t>吴十</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>1353085.67</v>
+        <v>997872.14</v>
       </c>
       <c r="D3" t="n">
-        <v>87861.33489999999</v>
+        <v>6902.971579999999</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>吴十</t>
+          <t>周九</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>964724.5199999999</v>
+        <v>1336041.12</v>
       </c>
       <c r="D4" t="n">
-        <v>62897.21595</v>
+        <v>83125.74567</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>孙八</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>1372501.78</v>
+        <v>379355.52</v>
       </c>
       <c r="D5" t="n">
-        <v>45903.5903</v>
+        <v>1934.503270000002</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -4751,42 +4809,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>周九</t>
+          <t>赵六</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>386903.61</v>
+        <v>1470821.29</v>
       </c>
       <c r="D6" t="n">
-        <v>34821.3249</v>
+        <v>53853.458465</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>李四</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>1277236.07</v>
+        <v>1397170.92</v>
       </c>
       <c r="D7" t="n">
-        <v>18058.5739</v>
+        <v>84527.910445</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -4795,45 +4853,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>钱七</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>1434332.64</v>
+        <v>966784.6000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>79797.3089</v>
+        <v>34768.67464</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>110245.47</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3307.3641</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
